--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/LT/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/LT/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingADV\LT\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9AFC5B-F1B7-4D35-9A83-A6D4D0FC2C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9A18E4-29F8-49B8-B2D9-657A9BA84AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="34">
   <si>
     <t>Dati originali</t>
   </si>
@@ -47,9 +47,6 @@
     <t>ERR</t>
   </si>
   <si>
-    <t>STD</t>
-  </si>
-  <si>
     <t>NOAUG</t>
   </si>
   <si>
@@ -116,21 +113,12 @@
     <t>LIST of BEST ERR 20%</t>
   </si>
   <si>
-    <t>tau=10%</t>
-  </si>
-  <si>
-    <t>eps=10^-6</t>
-  </si>
-  <si>
     <t>n=5 -&gt; 0.5 -&gt; 1</t>
   </si>
   <si>
     <t>n=5 -&gt; 1 -&gt; 1</t>
   </si>
   <si>
-    <t>eps=0.003</t>
-  </si>
-  <si>
     <t>ADV</t>
   </si>
   <si>
@@ -153,15 +141,6 @@
   </si>
   <si>
     <t>ep=0.001</t>
-  </si>
-  <si>
-    <t>ep=0.01</t>
-  </si>
-  <si>
-    <t>ep=0.1</t>
-  </si>
-  <si>
-    <t>EER0_STD</t>
   </si>
 </sst>
 </file>
@@ -480,232 +459,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
-        <v>3</v>
+      <c r="C2" s="1">
+        <v>33.166666666666664</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.4300112866673373</v>
+      </c>
+      <c r="E2" s="1">
+        <v>32</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.5345892868042634</v>
       </c>
       <c r="G2" s="1">
-        <v>33.166666666666664</v>
+        <v>12.777777777777779</v>
       </c>
       <c r="H2" s="1">
-        <v>4.4300112866673373</v>
+        <v>2.5630927498716187</v>
       </c>
       <c r="I2" s="1">
-        <v>32</v>
+        <v>25.981481481481481</v>
       </c>
       <c r="J2" s="1">
-        <v>4.5345892868042634</v>
+        <v>2.5020053685389105</v>
       </c>
       <c r="K2" s="1">
-        <v>12.777777777777779</v>
+        <v>13.203703703703702</v>
       </c>
       <c r="L2" s="1">
-        <v>2.5630927498716187</v>
-      </c>
-      <c r="M2" s="1">
-        <v>25.981481481481481</v>
-      </c>
-      <c r="N2" s="1">
-        <v>2.5020053685389105</v>
-      </c>
-      <c r="O2" s="1">
-        <v>13.203703703703702</v>
-      </c>
-      <c r="P2" s="1">
         <v>2.4885540449361203</v>
       </c>
-      <c r="R2">
-        <v>30.666666666666668</v>
-      </c>
-      <c r="S2">
-        <v>5.0579969684978323</v>
-      </c>
-      <c r="T2">
-        <v>30.666666666666668</v>
-      </c>
-      <c r="U2">
-        <v>4.5092497528228863</v>
-      </c>
-      <c r="V2">
-        <v>10.833333333333334</v>
-      </c>
-      <c r="W2">
-        <v>2.8431203515386652</v>
-      </c>
-      <c r="X2">
-        <v>24.055555555555557</v>
-      </c>
-      <c r="Y2">
-        <v>2.6943012562182544</v>
-      </c>
-      <c r="Z2">
-        <v>13.222222222222223</v>
-      </c>
-      <c r="AA2">
-        <v>4.3853713048590777</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1">
-        <v>27</v>
-      </c>
-      <c r="H5" s="1">
-        <v>6.3639610306789276</v>
-      </c>
-      <c r="I5" s="1">
-        <v>23</v>
-      </c>
-      <c r="J5" s="1">
-        <v>6.3639610306789276</v>
-      </c>
-      <c r="K5" s="1">
-        <v>11</v>
-      </c>
-      <c r="L5" s="1">
-        <v>2.1213203435596424</v>
-      </c>
-      <c r="M5" s="1">
-        <v>20.333333333333332</v>
-      </c>
-      <c r="N5" s="1">
-        <v>4.9497474683058327</v>
-      </c>
-      <c r="O5" s="1">
-        <v>9.3333333333333321</v>
-      </c>
-      <c r="P5" s="1">
-        <v>2.8284271247461903</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.70710678118654757</v>
-      </c>
-      <c r="I7" s="1">
-        <v>31.25</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1.0606601717798212</v>
-      </c>
-      <c r="K7" s="1">
-        <v>11</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2.1213203435596424</v>
-      </c>
-      <c r="M7" s="1">
-        <v>25.583333333333336</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0.8249579113843063</v>
-      </c>
-      <c r="O7" s="1">
-        <v>14.583333333333334</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1.2963624321753362</v>
-      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1">
+        <v>27.5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2.0736441353327719</v>
+      </c>
+      <c r="E4" s="1">
+        <v>26.416666666666668</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2.6536138880151094</v>
+      </c>
+      <c r="G4" s="1">
+        <v>11.333333333333334</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.9148542155126782</v>
+      </c>
+      <c r="I4" s="1">
+        <v>21.75</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.82158383625774922</v>
+      </c>
+      <c r="K4" s="1">
+        <v>10.416666666666666</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2.1775368347439494</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1">
+        <v>30.416666666666668</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4.2120857857677363</v>
+      </c>
+      <c r="E6" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4.2895221179054435</v>
+      </c>
+      <c r="G6" s="1">
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.9916492328386197</v>
+      </c>
+      <c r="I6" s="1">
+        <v>22.416666666666668</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.8521758975744052</v>
+      </c>
+      <c r="K6" s="1">
+        <v>14.083333333333334</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2.3015695127938613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -715,874 +646,511 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
-  <dimension ref="A1:AR15"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="34" max="34" width="26.88671875" customWidth="1"/>
     <col min="38" max="38" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="Q2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
       <c r="T2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="X2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="s">
         <v>15</v>
       </c>
-      <c r="AF2" t="s">
-        <v>16</v>
-      </c>
       <c r="AH2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="s">
         <v>1</v>
       </c>
       <c r="AJ2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM2" t="s">
         <v>1</v>
       </c>
       <c r="AN2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G3">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="H3">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I3">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="L3">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q3">
-        <f>AVERAGE(C3,D3)</f>
-        <v>34</v>
+        <f>AVERAGE(C3:D3)</f>
+        <v>36.5</v>
       </c>
       <c r="R3">
-        <f>AVERAGE(H3,I3)</f>
-        <v>32</v>
+        <f>AVERAGE(H3:I3)</f>
+        <v>28</v>
       </c>
       <c r="S3">
-        <f>AVERAGE(M3,N3)</f>
-        <v>12.5</v>
+        <f>AVERAGE(M3:N3)</f>
+        <v>10</v>
       </c>
       <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>26.166666666666668</v>
+        <v>24.833333333333332</v>
       </c>
       <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="V3">
-        <f>((T3-U3))</f>
-        <v>13.666666666666668</v>
+        <f>T3-U3</f>
+        <v>14.833333333333332</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q4)</f>
-        <v>34.5</v>
+        <f>AVERAGE(Q3:Q11)</f>
+        <v>30.416666666666668</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q4)</f>
-        <v>0.70710678118654757</v>
+        <f>_xlfn.STDEV.S(Q3:Q11)</f>
+        <v>4.2120857857677363</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R4)</f>
-        <v>31.25</v>
+        <f>AVERAGE(R3:R11)</f>
+        <v>28.5</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R4)</f>
-        <v>1.0606601717798212</v>
+        <f>_xlfn.STDEV.S(R3:R11)</f>
+        <v>4.2895221179054435</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S4)</f>
-        <v>11</v>
+        <f>AVERAGE(S3:S11)</f>
+        <v>8.3333333333333339</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S4)</f>
-        <v>2.1213203435596424</v>
+        <f>_xlfn.STDEV.S(S3:S11)</f>
+        <v>1.9916492328386197</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T4)</f>
-        <v>25.583333333333336</v>
+        <f>AVERAGE(T3:T11)</f>
+        <v>22.416666666666668</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T4)</f>
-        <v>0.8249579113843063</v>
+        <f>_xlfn.STDEV.S(T3:T11)</f>
+        <v>1.8521758975744052</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V4)</f>
-        <v>14.583333333333334</v>
+        <f>AVERAGE(V3:V11)</f>
+        <v>14.083333333333334</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V4)</f>
-        <v>1.2963624321753362</v>
+        <f>_xlfn.STDEV.S(V3:V11)</f>
+        <v>2.3015695127938613</v>
       </c>
       <c r="AH3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>73</v>
+      </c>
+      <c r="C4">
         <v>27</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="D4">
+        <v>33</v>
+      </c>
+      <c r="E4">
+        <v>67</v>
+      </c>
+      <c r="G4">
+        <v>66</v>
+      </c>
+      <c r="H4">
+        <v>34</v>
+      </c>
+      <c r="I4">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>73</v>
+      </c>
+      <c r="L4">
+        <v>96</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <v>17</v>
+      </c>
+      <c r="O4">
+        <v>83</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q8" si="0">AVERAGE(C4:D4)</f>
+        <v>30</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R8" si="1">AVERAGE(H4:I4)</f>
+        <v>30.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S8" si="2">AVERAGE(M4:N4)</f>
+        <v>10.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T8" si="3">AVERAGE(Q4:S4)</f>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U8" si="4">MIN(Q4:S4)</f>
+        <v>10.5</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V8" si="5">T4-U4</f>
+        <v>13.166666666666668</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>75</v>
+      </c>
+      <c r="G5">
+        <v>66</v>
+      </c>
+      <c r="H5">
+        <v>34</v>
+      </c>
+      <c r="I5">
+        <v>29</v>
+      </c>
+      <c r="J5">
+        <v>71</v>
+      </c>
+      <c r="L5">
+        <v>88</v>
+      </c>
+      <c r="M5">
+        <v>12</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>97</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>31.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>7.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>22.5</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>78</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>44</v>
+      </c>
+      <c r="E6">
+        <v>56</v>
+      </c>
+      <c r="G6">
+        <v>86</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>56</v>
-      </c>
-      <c r="C4">
-        <v>44</v>
-      </c>
-      <c r="D4">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>74</v>
-      </c>
-      <c r="G4">
-        <v>76</v>
-      </c>
-      <c r="H4">
-        <v>24</v>
-      </c>
-      <c r="I4">
-        <v>37</v>
-      </c>
-      <c r="J4">
-        <v>63</v>
-      </c>
-      <c r="L4">
-        <v>90</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4">
+      <c r="J6">
+        <v>72</v>
+      </c>
+      <c r="L6">
+        <v>91</v>
+      </c>
+      <c r="M6">
         <v>9</v>
       </c>
-      <c r="O4">
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6">
         <v>91</v>
       </c>
-      <c r="Q4">
-        <f t="shared" ref="Q4:Q9" si="0">AVERAGE(C4,D4)</f>
-        <v>35</v>
-      </c>
-      <c r="R4">
-        <f t="shared" ref="R4:R9" si="1">AVERAGE(H4,I4)</f>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>71</v>
+      </c>
+      <c r="G7">
+        <v>83</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>49</v>
+      </c>
+      <c r="J7">
+        <v>51</v>
+      </c>
+      <c r="L7">
+        <v>95</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>95</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
         <v>30.5</v>
       </c>
-      <c r="S4">
-        <f t="shared" ref="S4:S9" si="2">AVERAGE(M4,N4)</f>
-        <v>9.5</v>
-      </c>
-      <c r="T4">
-        <f t="shared" ref="T4:T9" si="3">AVERAGE(Q4:S4)</f>
-        <v>25</v>
-      </c>
-      <c r="U4">
-        <f t="shared" ref="U4:U9" si="4">MIN(Q4:S4)</f>
-        <v>9.5</v>
-      </c>
-      <c r="V4">
-        <f t="shared" ref="V4:V9" si="5">((T4-U4))</f>
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI4">
-        <v>28.041666666666668</v>
-      </c>
-      <c r="AJ4">
-        <v>2.5972222222222219</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM4">
-        <v>28.041666666666668</v>
-      </c>
-      <c r="AN4">
-        <v>2.5972222222222219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>17.833333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G8">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H8">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J8">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L8">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="S8">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>22.833333333333332</v>
+        <v>19.666666666666668</v>
       </c>
       <c r="U8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <f t="shared" si="5"/>
-        <v>9.8333333333333321</v>
-      </c>
-      <c r="W8">
-        <f>AVERAGE(Q8:Q11)</f>
-        <v>35.25</v>
-      </c>
-      <c r="X8">
-        <f>_xlfn.STDEV.S(Q8:Q11)</f>
-        <v>4.9916597106239795</v>
-      </c>
-      <c r="Y8">
-        <f>AVERAGE(R8:R11)</f>
-        <v>32.75</v>
-      </c>
-      <c r="Z8">
-        <f>_xlfn.STDEV.S(R8:R11)</f>
-        <v>5.3619026473818039</v>
-      </c>
-      <c r="AA8">
-        <f>AVERAGE(S8:S11)</f>
-        <v>11.625</v>
-      </c>
-      <c r="AB8">
-        <f>_xlfn.STDEV.S(S8:S11)</f>
-        <v>1.6007810593582121</v>
-      </c>
-      <c r="AC8">
-        <f>AVERAGE(T8:T11)</f>
-        <v>26.541666666666664</v>
-      </c>
-      <c r="AD8">
-        <f>_xlfn.STDEV.S(T8:T11)</f>
-        <v>2.7967408280459711</v>
-      </c>
-      <c r="AE8">
-        <f>AVERAGE(V8:V11)</f>
-        <v>14.916666666666664</v>
-      </c>
-      <c r="AF8">
-        <f>_xlfn.STDEV.S(V8:V11)</f>
-        <v>4.1510819651605919</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>58</v>
-      </c>
-      <c r="C9">
-        <v>42</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>58</v>
-      </c>
-      <c r="G9">
-        <v>71</v>
-      </c>
-      <c r="H9">
-        <v>29</v>
-      </c>
-      <c r="I9">
-        <v>43</v>
-      </c>
-      <c r="J9">
-        <v>57</v>
-      </c>
-      <c r="L9">
-        <v>90</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-      <c r="N9">
-        <v>11</v>
-      </c>
-      <c r="O9">
-        <v>89</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>10.5</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>29.5</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="4"/>
-        <v>10.5</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="5"/>
-        <v>19</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI9" t="e">
-        <f>AVERAGE(Q21:Q24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ9" t="e">
-        <f>_xlfn.STDEV.S(Q21:Q24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK9" t="e">
-        <f>AVERAGE(R21:R24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL9" t="e">
-        <f>_xlfn.STDEV.S(R21:R24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM9" t="e">
-        <f>AVERAGE(S21:S24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN9" t="e">
-        <f>_xlfn.STDEV.S(S21:S24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO9">
-        <v>28.041666666666668</v>
-      </c>
-      <c r="AP9">
-        <v>3.0103986446980731</v>
-      </c>
-      <c r="AQ9">
-        <v>2.5972222222222219</v>
-      </c>
-      <c r="AR9">
-        <v>0.62915286960589489</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>54</v>
-      </c>
-      <c r="C10">
-        <v>46</v>
-      </c>
-      <c r="D10">
-        <v>24</v>
-      </c>
-      <c r="E10">
-        <v>76</v>
-      </c>
-      <c r="G10">
-        <v>70</v>
-      </c>
-      <c r="H10">
-        <v>30</v>
-      </c>
-      <c r="I10">
-        <v>45</v>
-      </c>
-      <c r="J10">
-        <v>55</v>
-      </c>
-      <c r="L10">
-        <v>91</v>
-      </c>
-      <c r="M10">
-        <v>9</v>
-      </c>
-      <c r="N10">
-        <v>11</v>
-      </c>
-      <c r="O10">
-        <v>89</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" ref="Q10:Q15" si="6">AVERAGE(C10,D10)</f>
-        <v>35</v>
-      </c>
-      <c r="R10">
-        <f t="shared" ref="R10:R15" si="7">AVERAGE(H10,I10)</f>
-        <v>37.5</v>
-      </c>
-      <c r="S10">
-        <f t="shared" ref="S10:S15" si="8">AVERAGE(M10,N10)</f>
-        <v>10</v>
-      </c>
-      <c r="T10">
-        <f t="shared" ref="T10:T15" si="9">AVERAGE(Q10:S10)</f>
-        <v>27.5</v>
-      </c>
-      <c r="U10">
-        <f t="shared" ref="U10:U15" si="10">MIN(Q10:S10)</f>
-        <v>10</v>
-      </c>
-      <c r="V10">
-        <f t="shared" ref="V10:V15" si="11">((T10-U10))</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>66</v>
-      </c>
-      <c r="C11">
-        <v>34</v>
-      </c>
-      <c r="D11">
-        <v>34</v>
-      </c>
-      <c r="E11">
-        <v>66</v>
-      </c>
-      <c r="G11">
-        <v>65</v>
-      </c>
-      <c r="H11">
-        <v>35</v>
-      </c>
-      <c r="I11">
-        <v>29</v>
-      </c>
-      <c r="J11">
-        <v>71</v>
-      </c>
-      <c r="L11">
-        <v>86</v>
-      </c>
-      <c r="M11">
-        <v>14</v>
-      </c>
-      <c r="N11">
-        <v>12</v>
-      </c>
-      <c r="O11">
-        <v>88</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="7"/>
-        <v>32</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="9"/>
-        <v>26.333333333333332</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="11"/>
-        <v>13.333333333333332</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>48</v>
-      </c>
-      <c r="C13">
-        <v>52</v>
-      </c>
-      <c r="D13">
-        <v>38</v>
-      </c>
-      <c r="E13">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>68</v>
-      </c>
-      <c r="H13">
-        <v>32</v>
-      </c>
-      <c r="I13">
-        <v>38</v>
-      </c>
-      <c r="J13">
-        <v>62</v>
-      </c>
-      <c r="L13">
-        <v>89</v>
-      </c>
-      <c r="M13">
-        <v>11</v>
-      </c>
-      <c r="N13">
-        <v>15</v>
-      </c>
-      <c r="O13">
-        <v>85</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="7"/>
-        <v>35</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="W13">
-        <f>AVERAGE(Q13:Q15)</f>
-        <v>34.333333333333336</v>
-      </c>
-      <c r="X13">
-        <f>_xlfn.STDEV.S(Q13:Q15)</f>
-        <v>9.2511260575852745</v>
-      </c>
-      <c r="Y13">
-        <f>AVERAGE(R13:R15)</f>
-        <v>35</v>
-      </c>
-      <c r="Z13">
-        <f>_xlfn.STDEV.S(R13:R15)</f>
-        <v>2.5</v>
-      </c>
-      <c r="AA13">
-        <f>AVERAGE(S13:S15)</f>
-        <v>11.833333333333334</v>
-      </c>
-      <c r="AB13">
-        <f>_xlfn.STDEV.S(S13:S15)</f>
-        <v>1.2583057392117918</v>
-      </c>
-      <c r="AC13">
-        <f>AVERAGE(T13:T15)</f>
-        <v>27.055555555555557</v>
-      </c>
-      <c r="AD13">
-        <f>_xlfn.STDEV.S(T13:T15)</f>
-        <v>3.441306814655209</v>
-      </c>
-      <c r="AE13">
-        <f>AVERAGE(V13:V15)</f>
-        <v>15.222222222222223</v>
-      </c>
-      <c r="AF13">
-        <f>_xlfn.STDEV.S(V13:V15)</f>
-        <v>2.6736020923368713</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>67</v>
-      </c>
-      <c r="C14">
-        <v>33</v>
-      </c>
-      <c r="D14">
-        <v>26</v>
-      </c>
-      <c r="E14">
-        <v>74</v>
-      </c>
-      <c r="G14">
-        <v>65</v>
-      </c>
-      <c r="H14">
-        <v>35</v>
-      </c>
-      <c r="I14">
-        <v>30</v>
-      </c>
-      <c r="J14">
-        <v>70</v>
-      </c>
-      <c r="L14">
-        <v>88</v>
-      </c>
-      <c r="M14">
-        <v>12</v>
-      </c>
-      <c r="N14">
-        <v>12</v>
-      </c>
-      <c r="O14">
-        <v>88</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="6"/>
-        <v>29.5</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="7"/>
-        <v>32.5</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="9"/>
-        <v>24.666666666666668</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="11"/>
-        <v>12.666666666666668</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>61</v>
-      </c>
-      <c r="C15">
-        <v>39</v>
-      </c>
-      <c r="D15">
-        <v>18</v>
-      </c>
-      <c r="E15">
-        <v>82</v>
-      </c>
-      <c r="G15">
-        <v>53</v>
-      </c>
-      <c r="H15">
-        <v>47</v>
-      </c>
-      <c r="I15">
-        <v>28</v>
-      </c>
-      <c r="J15">
-        <v>72</v>
-      </c>
-      <c r="L15">
-        <v>85</v>
-      </c>
-      <c r="M15">
-        <v>15</v>
-      </c>
-      <c r="N15">
-        <v>6</v>
-      </c>
-      <c r="O15">
-        <v>94</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="6"/>
-        <v>28.5</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="7"/>
-        <v>37.5</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="8"/>
-        <v>10.5</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="9"/>
-        <v>25.5</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="10"/>
-        <v>10.5</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="11"/>
-        <v>15</v>
+        <v>11.666666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -1592,306 +1160,345 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="34" max="34" width="26.88671875" customWidth="1"/>
     <col min="38" max="38" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="Q2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
       <c r="T2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="X2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="s">
         <v>15</v>
       </c>
-      <c r="AF2" t="s">
-        <v>16</v>
-      </c>
       <c r="AH2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="s">
         <v>1</v>
       </c>
       <c r="AJ2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM2" t="s">
         <v>1</v>
       </c>
       <c r="AN2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="G3">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J3">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L3">
+        <v>81</v>
+      </c>
+      <c r="M3">
+        <v>19</v>
+      </c>
+      <c r="N3">
+        <v>7</v>
+      </c>
+      <c r="O3">
         <v>93</v>
       </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-      <c r="N3">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>81</v>
-      </c>
       <c r="Q3">
-        <f>AVERAGE(C3,D3)</f>
-        <v>34.5</v>
+        <f>AVERAGE(C3:D3)</f>
+        <v>26</v>
       </c>
       <c r="R3">
-        <f>AVERAGE(H3,I3)</f>
-        <v>25.5</v>
+        <f>AVERAGE(H3:I3)</f>
+        <v>22</v>
       </c>
       <c r="S3">
-        <f>AVERAGE(M3,N3)</f>
+        <f>AVERAGE(M3:N3)</f>
         <v>13</v>
       </c>
       <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>24.333333333333332</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="U3">
         <f>MIN(Q3:S3)</f>
         <v>13</v>
       </c>
       <c r="V3">
-        <f>((T3-U3))</f>
-        <v>11.333333333333332</v>
+        <f>T3-U3</f>
+        <v>7.3333333333333321</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q4)</f>
-        <v>39.25</v>
+        <f>AVERAGE(Q3:Q11)</f>
+        <v>27.5</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q4)</f>
-        <v>6.7175144212722016</v>
+        <f>_xlfn.STDEV.S(Q3:Q11)</f>
+        <v>2.0736441353327719</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R4)</f>
-        <v>30.5</v>
+        <f>AVERAGE(R3:R11)</f>
+        <v>26.416666666666668</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R4)</f>
-        <v>7.0710678118654755</v>
+        <f>_xlfn.STDEV.S(R3:R11)</f>
+        <v>2.6536138880151094</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S4)</f>
-        <v>11.75</v>
+        <f>AVERAGE(S3:S11)</f>
+        <v>11.333333333333334</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S4)</f>
-        <v>1.7677669529663689</v>
+        <f>_xlfn.STDEV.S(S3:S11)</f>
+        <v>1.9148542155126782</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T4)</f>
-        <v>27.166666666666664</v>
+        <f>AVERAGE(T3:T11)</f>
+        <v>21.75</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T4)</f>
-        <v>4.00693842672381</v>
+        <f>_xlfn.STDEV.S(T3:T11)</f>
+        <v>0.82158383625774922</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V4)</f>
-        <v>15.416666666666666</v>
+        <f>AVERAGE(V3:V11)</f>
+        <v>10.416666666666666</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V4)</f>
-        <v>5.7747053796901433</v>
+        <f>_xlfn.STDEV.S(V3:V11)</f>
+        <v>2.1775368347439494</v>
       </c>
       <c r="AH3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>77</v>
+      </c>
+      <c r="C4">
+        <v>23</v>
+      </c>
+      <c r="D4">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>42</v>
-      </c>
-      <c r="C4">
-        <v>58</v>
-      </c>
-      <c r="D4">
+      <c r="E4">
+        <v>72</v>
+      </c>
+      <c r="G4">
+        <v>81</v>
+      </c>
+      <c r="H4">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>38</v>
+      </c>
+      <c r="J4">
+        <v>62</v>
+      </c>
+      <c r="L4">
+        <v>88</v>
+      </c>
+      <c r="M4">
+        <v>12</v>
+      </c>
+      <c r="N4">
+        <v>7</v>
+      </c>
+      <c r="O4">
+        <v>93</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q8" si="0">AVERAGE(C4:D4)</f>
+        <v>25.5</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R8" si="1">AVERAGE(H4:I4)</f>
+        <v>28.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S8" si="2">AVERAGE(M4:N4)</f>
+        <v>9.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T8" si="3">AVERAGE(Q4:S4)</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U8" si="4">MIN(Q4:S4)</f>
+        <v>9.5</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V8" si="5">T4-U4</f>
+        <v>11.666666666666668</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>77</v>
+      </c>
+      <c r="G5">
+        <v>83</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>39</v>
+      </c>
+      <c r="J5">
+        <v>61</v>
+      </c>
+      <c r="L5">
+        <v>91</v>
+      </c>
+      <c r="M5">
+        <v>9</v>
+      </c>
+      <c r="N5">
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <v>92</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="E4">
-        <v>70</v>
-      </c>
-      <c r="G4">
-        <v>61</v>
-      </c>
-      <c r="H4">
-        <v>39</v>
-      </c>
-      <c r="I4">
-        <v>32</v>
-      </c>
-      <c r="J4">
-        <v>68</v>
-      </c>
-      <c r="L4">
-        <v>85</v>
-      </c>
-      <c r="M4">
-        <v>15</v>
-      </c>
-      <c r="N4">
-        <v>6</v>
-      </c>
-      <c r="O4">
-        <v>94</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" ref="Q4:Q10" si="0">AVERAGE(C4,D4)</f>
-        <v>44</v>
-      </c>
-      <c r="R4">
-        <f t="shared" ref="R4:R10" si="1">AVERAGE(H4,I4)</f>
-        <v>35.5</v>
-      </c>
-      <c r="S4">
-        <f t="shared" ref="S4:S10" si="2">AVERAGE(M4,N4)</f>
-        <v>10.5</v>
-      </c>
-      <c r="T4">
-        <f t="shared" ref="T4:T10" si="3">AVERAGE(Q4:S4)</f>
-        <v>30</v>
-      </c>
-      <c r="U4">
-        <f t="shared" ref="U4:U10" si="4">MIN(Q4:S4)</f>
-        <v>10.5</v>
-      </c>
-      <c r="V4">
-        <f t="shared" ref="V4:V10" si="5">((T4-U4))</f>
-        <v>19.5</v>
-      </c>
-      <c r="AH4" t="s">
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>8.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>13.666666666666668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>72</v>
+      </c>
+      <c r="C6">
+        <v>28</v>
+      </c>
+      <c r="D6">
         <v>29</v>
       </c>
-      <c r="AI4">
-        <v>28.041666666666668</v>
-      </c>
-      <c r="AJ4">
-        <v>2.5972222222222219</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM4">
-        <v>28.041666666666668</v>
-      </c>
-      <c r="AN4">
-        <v>2.5972222222222219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>63</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>31</v>
-      </c>
       <c r="E6">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H6">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>33</v>
@@ -1900,24 +1507,24 @@
         <v>67</v>
       </c>
       <c r="L6">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>28.5</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="S6">
         <f t="shared" si="2"/>
@@ -1925,7 +1532,7 @@
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>27.666666666666668</v>
+        <v>22.166666666666668</v>
       </c>
       <c r="U6">
         <f t="shared" si="4"/>
@@ -1933,347 +1540,131 @@
       </c>
       <c r="V6">
         <f t="shared" si="5"/>
-        <v>14.666666666666668</v>
-      </c>
-      <c r="W6">
-        <f>AVERAGE(Q6:Q7)</f>
-        <v>34.25</v>
-      </c>
-      <c r="X6">
-        <f>_xlfn.STDEV.S(Q6:Q7)</f>
-        <v>0.35355339059327379</v>
-      </c>
-      <c r="Y6">
-        <f>AVERAGE(R6:R7)</f>
-        <v>34.5</v>
-      </c>
-      <c r="Z6">
-        <f>_xlfn.STDEV.S(R6:R7)</f>
-        <v>2.1213203435596424</v>
-      </c>
-      <c r="AA6">
-        <f>AVERAGE(S6:S7)</f>
-        <v>14</v>
-      </c>
-      <c r="AB6">
-        <f>_xlfn.STDEV.S(S6:S7)</f>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="AC6">
-        <f>AVERAGE(T6:T7)</f>
-        <v>27.583333333333336</v>
-      </c>
-      <c r="AD6">
-        <f>_xlfn.STDEV.S(T6:T7)</f>
-        <v>0.11785113019775875</v>
-      </c>
-      <c r="AE6">
-        <f>AVERAGE(V6:V7)</f>
-        <v>13.583333333333334</v>
-      </c>
-      <c r="AF6">
-        <f>_xlfn.STDEV.S(V6:V7)</f>
-        <v>1.5320646925708539</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR6" t="s">
+        <v>9.1666666666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>70</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>71</v>
+      </c>
+      <c r="H7">
+        <v>29</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>71</v>
+      </c>
+      <c r="L7">
+        <v>91</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+      <c r="N7">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>53</v>
-      </c>
-      <c r="C7">
-        <v>47</v>
-      </c>
-      <c r="D7">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>78</v>
-      </c>
-      <c r="G7">
-        <v>67</v>
-      </c>
-      <c r="H7">
-        <v>33</v>
-      </c>
-      <c r="I7">
-        <v>33</v>
-      </c>
-      <c r="J7">
-        <v>67</v>
-      </c>
-      <c r="L7">
-        <v>82</v>
-      </c>
-      <c r="M7">
-        <v>18</v>
-      </c>
-      <c r="N7">
-        <v>12</v>
-      </c>
       <c r="O7">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>25.5</v>
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S7">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>27.5</v>
+        <v>22.333333333333332</v>
       </c>
       <c r="U7">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="V7">
         <f t="shared" si="5"/>
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI7" t="e">
-        <f>AVERAGE(Q17:Q20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ7" t="e">
-        <f>_xlfn.STDEV.S(Q17:Q20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK7" t="e">
-        <f>AVERAGE(R17:R20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL7" t="e">
-        <f>_xlfn.STDEV.S(R17:R20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM7" t="e">
-        <f>AVERAGE(S17:S20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN7" t="e">
-        <f>_xlfn.STDEV.S(S17:S20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO7">
-        <v>28.041666666666668</v>
-      </c>
-      <c r="AP7">
-        <v>3.0103986446980731</v>
-      </c>
-      <c r="AQ7">
-        <v>2.5972222222222219</v>
-      </c>
-      <c r="AR7">
-        <v>0.62915286960589489</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>66</v>
-      </c>
-      <c r="C9">
-        <v>34</v>
-      </c>
-      <c r="D9">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>71</v>
-      </c>
-      <c r="G9">
-        <v>77</v>
-      </c>
-      <c r="H9">
-        <v>23</v>
-      </c>
-      <c r="I9">
-        <v>32</v>
-      </c>
-      <c r="J9">
-        <v>68</v>
-      </c>
-      <c r="L9">
-        <v>85</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-      <c r="N9">
-        <v>10</v>
-      </c>
-      <c r="O9">
-        <v>90</v>
-      </c>
-      <c r="Q9">
+        <v>9.8333333333333321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>59</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>82</v>
+      </c>
+      <c r="G8">
+        <v>70</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>22</v>
+      </c>
+      <c r="J8">
+        <v>78</v>
+      </c>
+      <c r="L8">
+        <v>82</v>
+      </c>
+      <c r="M8">
+        <v>18</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>95</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="0"/>
-        <v>31.5</v>
-      </c>
-      <c r="R9">
+        <v>29.5</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="1"/>
-        <v>27.5</v>
-      </c>
-      <c r="S9">
+        <v>26</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="2"/>
-        <v>12.5</v>
-      </c>
-      <c r="T9">
+        <v>11.5</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="3"/>
-        <v>23.833333333333332</v>
-      </c>
-      <c r="U9">
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U8">
         <f t="shared" si="4"/>
-        <v>12.5</v>
-      </c>
-      <c r="V9">
+        <v>11.5</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="5"/>
-        <v>11.333333333333332</v>
-      </c>
-      <c r="W9">
-        <f>AVERAGE(Q9:Q10)</f>
-        <v>27</v>
-      </c>
-      <c r="X9">
-        <f>_xlfn.STDEV.S(Q9:Q10)</f>
-        <v>6.3639610306789276</v>
-      </c>
-      <c r="Y9">
-        <f>AVERAGE(R9:R10)</f>
-        <v>23</v>
-      </c>
-      <c r="Z9">
-        <f>_xlfn.STDEV.S(R9:R10)</f>
-        <v>6.3639610306789276</v>
-      </c>
-      <c r="AA9">
-        <f>AVERAGE(S9:S10)</f>
-        <v>11</v>
-      </c>
-      <c r="AB9">
-        <f>_xlfn.STDEV.S(S9:S10)</f>
-        <v>2.1213203435596424</v>
-      </c>
-      <c r="AC9">
-        <f>AVERAGE(T9:T10)</f>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="AD9">
-        <f>_xlfn.STDEV.S(T9:T10)</f>
-        <v>4.9497474683058327</v>
-      </c>
-      <c r="AE9">
-        <f>AVERAGE(V9:V10)</f>
-        <v>9.3333333333333321</v>
-      </c>
-      <c r="AF9">
-        <f>_xlfn.STDEV.S(V9:V10)</f>
-        <v>2.8284271247461903</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>68</v>
-      </c>
-      <c r="C10">
-        <v>32</v>
-      </c>
-      <c r="D10">
-        <v>13</v>
-      </c>
-      <c r="E10">
-        <v>87</v>
-      </c>
-      <c r="G10">
-        <v>89</v>
-      </c>
-      <c r="H10">
-        <v>11</v>
-      </c>
-      <c r="I10">
-        <v>26</v>
-      </c>
-      <c r="J10">
-        <v>74</v>
-      </c>
-      <c r="L10">
-        <v>90</v>
-      </c>
-      <c r="M10">
-        <v>10</v>
-      </c>
-      <c r="N10">
-        <v>9</v>
-      </c>
-      <c r="O10">
-        <v>91</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="1"/>
-        <v>18.5</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="2"/>
-        <v>9.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="3"/>
-        <v>16.833333333333332</v>
-      </c>
-      <c r="U10">
-        <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="5"/>
-        <v>7.3333333333333321</v>
+        <v>10.833333333333332</v>
       </c>
     </row>
   </sheetData>
@@ -2295,60 +1686,60 @@
         <v>0</v>
       </c>
       <c r="Q1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
       <c r="T2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="X2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="s">
         <v>15</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
